--- a/excel/ServidoCorral.xlsx
+++ b/excel/ServidoCorral.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -48,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,8 +413,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -464,376 +472,6 @@
         <is>
           <t>Fecha Servida</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>F-000001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>A-1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>AGOSTADERO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LISTO</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>150</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>46061.62152777778</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>46071.85416666666</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>4</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>F-000004</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>A-2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AGOSTADERO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>LISTO</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>150</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>46061.62222222222</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>46071.85416666666</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>F-000005</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>A-3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AGOSTADERO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LISTO</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>150</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>46061.62222222222</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>46071.85416666666</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>F-000006</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>A-4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AGOSTADERO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LISTO</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>180</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>46061.62222222222</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>46071.85416666666</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>F-000007</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>A-5</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AGOSTADERO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LISTO</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>190</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>46061.62222222222</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>46071.85416666666</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>F-000008</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>B-1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>AGOSTADERO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LISTO</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>200</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>46061.87430555555</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>46071.85416666666</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>F-000009</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>B-2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>AGOSTADERO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>LISTO</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>250</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>46061.87430555555</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>46071.85416666666</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>F-000010</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>B-3</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>AGOSTADERO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LISTO</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>200</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>46061.87430555555</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>46071.85416666666</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>F-000011</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>B-4</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>AGOSTADERO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LISTO</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>200</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>46061.87430555555</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>46071.85416666666</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>12</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>F-000012</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>B-5</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>AGOSTADERO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LISTO</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>200</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>46061.87430555555</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>46071.85416666666</v>
       </c>
     </row>
   </sheetData>
